--- a/data/indonesia_model_inputs.xlsx
+++ b/data/indonesia_model_inputs.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/wrgg_uw_edu/Documents/02Work/WorldBank-Indonesia/uw-wb-indonesia-ncd/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_0C710D44475D1BAD4A588195A28C8E47DB0B7F50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4580B05-CC0E-43C9-9064-322DEC044C63}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_0C710D44475D1BAD4A588195A28C8E47DB0B7F50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8523B379-E550-4158-B9D4-5582EA6E3F24}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Assumptions" sheetId="2" r:id="rId2"/>
-    <sheet name="Dictionaries" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="Intervention_Cause_Map" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Dictionaries" sheetId="3" r:id="rId3"/>
+    <sheet name="Intervention_Cause_Map" sheetId="4" r:id="rId4"/>
     <sheet name="Effect_Sizes" sheetId="5" r:id="rId5"/>
     <sheet name="Coverage" sheetId="6" r:id="rId6"/>
     <sheet name="Cost_Components" sheetId="7" r:id="rId7"/>
     <sheet name="Model_Input_View" sheetId="8" r:id="rId8"/>
-    <sheet name="FairChoices_Methods" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet name="Scope_and_Sources" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet name="QA_Checks" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet name="FairChoices_Methods" sheetId="9" r:id="rId9"/>
+    <sheet name="Scope_and_Sources" sheetId="10" r:id="rId10"/>
+    <sheet name="QA_Checks" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2279,20 +2279,26 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2315,26 +2321,20 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3192,38 +3192,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
+      <c r="A3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
@@ -3236,54 +3236,54 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69" t="s">
+      <c r="B5" s="57"/>
+      <c r="C5" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69" t="s">
+      <c r="D5" s="57"/>
+      <c r="E5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69" t="s">
+      <c r="F5" s="57"/>
+      <c r="G5" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="69"/>
+      <c r="H5" s="57"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="70" t="str">
+      <c r="A6" s="58" t="str">
         <f>IF(COUNTIF(QA_Checks!$E$2:$E$9,"FAIL")=0,"READY TO RUN","REVIEW REQUIRED")</f>
         <v>REVIEW REQUIRED</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="70">
+      <c r="B6" s="59"/>
+      <c r="C6" s="58">
         <f>COUNTA(Dictionaries!$A$2:$A$9)</f>
         <v>8</v>
       </c>
-      <c r="D6" s="71"/>
-      <c r="E6" s="70">
+      <c r="D6" s="59"/>
+      <c r="E6" s="58">
         <f>COUNTIF(Dictionaries!$I$2:$I$9,1)</f>
         <v>7</v>
       </c>
-      <c r="F6" s="71"/>
-      <c r="G6" s="70">
+      <c r="F6" s="59"/>
+      <c r="G6" s="58">
         <f>COUNTA(Intervention_Cause_Map!$A$2:$A$18)</f>
         <v>17</v>
       </c>
-      <c r="H6" s="71"/>
+      <c r="H6" s="59"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="72"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="73"/>
+      <c r="A7" s="60"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="61"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1"/>
@@ -3296,86 +3296,86 @@
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
     </row>
     <row r="10" spans="1:8" ht="28.05" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="63"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="65"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="66"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="68"/>
     </row>
     <row r="12" spans="1:8" ht="28.05" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="66"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="68"/>
     </row>
     <row r="13" spans="1:8" ht="28.05" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="68"/>
     </row>
     <row r="14" spans="1:8" ht="28.05" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="59"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="73"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
@@ -3388,86 +3388,86 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
     </row>
     <row r="17" spans="1:8" ht="28.05" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
     </row>
     <row r="18" spans="1:8" ht="28.05" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="55" t="s">
+      <c r="B18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
     </row>
     <row r="19" spans="1:8" ht="28.05" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
     </row>
     <row r="20" spans="1:8" ht="28.05" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
     </row>
     <row r="21" spans="1:8" ht="28.05" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1"/>
@@ -3480,19 +3480,32 @@
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B13:H13"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:B5"/>
@@ -3503,19 +3516,6 @@
     <mergeCell ref="E6:F7"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H7"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11331,7 +11331,7 @@
         <v>0.56756756756756754</v>
       </c>
       <c r="L3" s="36">
-        <f t="shared" si="1"/>
+        <f>IF(K3="","",K3*G3)</f>
         <v>0.56756756756756754</v>
       </c>
       <c r="M3" s="25" t="s">
@@ -11457,7 +11457,7 @@
         <v>0.49000000000000005</v>
       </c>
       <c r="K5" s="36">
-        <f t="shared" si="2"/>
+        <f>IF(OR(H5="",F5=""),"",F5*J5/(1-F5*H5))</f>
         <v>0.31779966370405965</v>
       </c>
       <c r="L5" s="36">

--- a/data/indonesia_model_inputs.xlsx
+++ b/data/indonesia_model_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/wrgg_uw_edu/Documents/02Work/WorldBank-Indonesia/uw-wb-indonesia-ncd/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_0C710D44475D1BAD4A588195A28C8E47DB0B7F50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8523B379-E550-4158-B9D4-5582EA6E3F24}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_0C710D44475D1BAD4A588195A28C8E47DB0B7F50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{750E90AA-655D-4094-A57B-B11ABC5631F6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="FairChoices_Methods" sheetId="9" r:id="rId9"/>
     <sheet name="Scope_and_Sources" sheetId="10" r:id="rId10"/>
     <sheet name="QA_Checks" sheetId="11" r:id="rId11"/>
+    <sheet name="ChangesLog" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,8 +43,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={65F284AB-064D-4B9D-A390-F156B89E3B37}</author>
+  </authors>
+  <commentList>
+    <comment ref="S33" authorId="0" shapeId="0" xr:uid="{65F284AB-064D-4B9D-A390-F156B89E3B37}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Pending update with Sali Info</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="594">
   <si>
     <t>Indonesia NCD model — user input workbook</t>
   </si>
@@ -1807,6 +1826,24 @@
   </si>
   <si>
     <t>Only selected base-case cost rows are model-ready</t>
+  </si>
+  <si>
+    <t>RHD</t>
+  </si>
+  <si>
+    <t>Cause</t>
+  </si>
+  <si>
+    <t>Intervention</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Since we do not have svere state, the PIN is updated to 9 % based on the RHD detailed model from The Uganda/Indonesia modelling</t>
   </si>
 </sst>
 </file>
@@ -1817,7 +1854,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1881,6 +1918,17 @@
       <i/>
       <sz val="9"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -2115,7 +2163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2279,26 +2327,20 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2321,23 +2363,42 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2751,6 +2812,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="William R Garcia" id="{08755B68-3142-46D3-BD70-CECE36D4D0BB}" userId="S::wrgg@uw.edu::52698913-8803-44d0-b81a-d207944fdb38" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3178,6 +3245,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="S33" dT="2026-08-20T17:22:41.38" personId="{08755B68-3142-46D3-BD70-CECE36D4D0BB}" id="{65F284AB-064D-4B9D-A390-F156B89E3B37}">
+    <text>Pending update with Sali Info</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H23"/>
@@ -3192,38 +3267,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="A3" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
@@ -3236,54 +3311,54 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57" t="s">
+      <c r="B5" s="69"/>
+      <c r="C5" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57" t="s">
+      <c r="D5" s="69"/>
+      <c r="E5" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57" t="s">
+      <c r="F5" s="69"/>
+      <c r="G5" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="57"/>
+      <c r="H5" s="69"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="58" t="str">
+      <c r="A6" s="70" t="str">
         <f>IF(COUNTIF(QA_Checks!$E$2:$E$9,"FAIL")=0,"READY TO RUN","REVIEW REQUIRED")</f>
         <v>REVIEW REQUIRED</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="58">
+      <c r="B6" s="71"/>
+      <c r="C6" s="70">
         <f>COUNTA(Dictionaries!$A$2:$A$9)</f>
         <v>8</v>
       </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="58">
+      <c r="D6" s="71"/>
+      <c r="E6" s="70">
         <f>COUNTIF(Dictionaries!$I$2:$I$9,1)</f>
         <v>7</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="58">
+      <c r="F6" s="71"/>
+      <c r="G6" s="70">
         <f>COUNTA(Intervention_Cause_Map!$A$2:$A$18)</f>
         <v>17</v>
       </c>
-      <c r="H6" s="59"/>
+      <c r="H6" s="71"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="60"/>
-      <c r="B7" s="61"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="61"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="73"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1"/>
@@ -3296,86 +3371,86 @@
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
     </row>
     <row r="10" spans="1:8" ht="28.05" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="65"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="63"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="68"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="66"/>
     </row>
     <row r="12" spans="1:8" ht="28.05" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="68"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="66"/>
     </row>
     <row r="13" spans="1:8" ht="28.05" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="68"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="66"/>
     </row>
     <row r="14" spans="1:8" ht="28.05" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="73"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="59"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
@@ -3388,86 +3463,86 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="62" t="s">
+      <c r="A16" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
     </row>
     <row r="17" spans="1:8" ht="28.05" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
     </row>
     <row r="18" spans="1:8" ht="28.05" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
     </row>
     <row r="19" spans="1:8" ht="28.05" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:8" ht="28.05" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:8" ht="28.05" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1"/>
@@ -3480,32 +3555,19 @@
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="70" t="s">
+      <c r="A23" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B13:H13"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:B5"/>
@@ -3516,6 +3578,19 @@
     <mergeCell ref="E6:F7"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3874,11 +3949,11 @@
       </c>
       <c r="D4" s="54">
         <f>COUNTIF(Coverage!$S$2:$S$18,"&lt;&gt;OK")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="54" t="str">
         <f t="shared" si="0"/>
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>572</v>
@@ -3896,7 +3971,7 @@
       </c>
       <c r="D5" s="54">
         <f>COUNTIF(Cost_Components!$AC$2:$AC$35,"&lt;&gt;OK")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="54" t="str">
         <f t="shared" si="0"/>
@@ -4005,6 +4080,47 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F251E35-2D95-4CA4-949B-9CA41039AC58}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="2" max="2" width="17.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="75">
+        <v>46254</v>
+      </c>
+      <c r="D2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5635,7 +5751,7 @@
         <v>0.75</v>
       </c>
       <c r="K3" s="14">
-        <v>1</v>
+        <v>0.09</v>
       </c>
       <c r="L3" s="33">
         <v>5</v>
@@ -7787,7 +7903,9 @@
       <c r="F17" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="G17" s="14"/>
+      <c r="G17" s="76">
+        <v>0.31</v>
+      </c>
       <c r="H17" s="14"/>
       <c r="I17" s="36">
         <f>IF(H17="",Assumptions!$B$5,H17)</f>
@@ -7812,9 +7930,9 @@
       <c r="P17" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="Q17" s="36" t="str">
+      <c r="Q17" s="36">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0.49000000000000005</v>
       </c>
       <c r="R17" s="25">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$18,B17)</f>
@@ -7822,7 +7940,7 @@
       </c>
       <c r="S17" s="25" t="str">
         <f t="shared" si="1"/>
-        <v>MISSING BASELINE</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="22.8">
@@ -7844,7 +7962,9 @@
       <c r="F18" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="G18" s="31"/>
+      <c r="G18" s="76">
+        <v>0.31</v>
+      </c>
       <c r="H18" s="31"/>
       <c r="I18" s="37">
         <f>IF(H18="",Assumptions!$B$5,H18)</f>
@@ -7869,9 +7989,9 @@
       <c r="P18" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="Q18" s="37" t="str">
+      <c r="Q18" s="37">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0.49000000000000005</v>
       </c>
       <c r="R18" s="26">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$18,B18)</f>
@@ -7879,7 +7999,7 @@
       </c>
       <c r="S18" s="26" t="str">
         <f t="shared" si="1"/>
-        <v>MISSING BASELINE</v>
+        <v>OK</v>
       </c>
     </row>
   </sheetData>
@@ -7903,7 +8023,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AC35"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
@@ -10862,8 +10982,8 @@
       <c r="C33" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="33">
-        <v>0</v>
+      <c r="D33" s="78">
+        <v>1</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>118</v>
@@ -10907,7 +11027,9 @@
       <c r="R33" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="S33" s="42"/>
+      <c r="S33" s="77">
+        <v>7</v>
+      </c>
       <c r="T33" s="12">
         <v>2023</v>
       </c>
@@ -10933,11 +11055,11 @@
       </c>
       <c r="AB33" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" s="25" t="str">
-        <f t="shared" si="1"/>
-        <v>MISSING COST</v>
+        <f>IF(AA33&lt;1,"BAD KEY",IF(S33="","MISSING COST",IF(U33=0,"REVIEW ADJUSTMENT",IF(AB33&lt;&gt;1,"CHECK SELECTION","OK"))))</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -11040,7 +11162,7 @@
       <c r="C35" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="79">
         <v>1</v>
       </c>
       <c r="E35" s="10" t="s">
@@ -11118,7 +11240,7 @@
         <v>1</v>
       </c>
       <c r="AC35" s="26" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(AA35&lt;1,"BAD KEY",IF(S35="","MISSING COST",IF(U35=0,"REVIEW ADJUSTMENT",IF(AB35&lt;&gt;1,"CHECK SELECTION","OK"))))</f>
         <v>REVIEW ADJUSTMENT</v>
       </c>
     </row>
@@ -11141,8 +11263,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11312,7 +11435,7 @@
       </c>
       <c r="G3" s="36">
         <f>SUMIF(Effect_Sizes!$B$2:$B$18,A3,Effect_Sizes!$K$2:$K$18)</f>
-        <v>1</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="36">
         <f>SUMIF(Coverage!$B$2:$B$18,A3,Coverage!$G$2:$G$18)</f>
@@ -11332,7 +11455,7 @@
       </c>
       <c r="L3" s="36">
         <f>IF(K3="","",K3*G3)</f>
-        <v>0.56756756756756754</v>
+        <v>5.108108108108108E-2</v>
       </c>
       <c r="M3" s="25" t="s">
         <v>142</v>
@@ -12057,11 +12180,11 @@
       </c>
       <c r="O14" s="39">
         <f>COUNTIFS(Cost_Components!$G$2:$G$35,M14,Cost_Components!$D$2:$D$35,1)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14" s="45">
         <f>SUMIFS(Cost_Components!$S$2:$S$35,Cost_Components!$G$2:$G$35,M14,Cost_Components!$D$2:$D$35,1)</f>
-        <v>34.349530000000001</v>
+        <v>41.349530000000001</v>
       </c>
       <c r="Q14" s="25" t="str">
         <f>IF(H14=0,"MISSING COVERAGE",IF(O14=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$18,A14)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -12226,7 +12349,7 @@
       </c>
       <c r="H17" s="36">
         <f>SUMIF(Coverage!$B$2:$B$18,A17,Coverage!$G$2:$G$18)</f>
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I17" s="36">
         <f>SUMIF(Coverage!$B$2:$B$18,A17,Coverage!$I$2:$I$18)</f>
@@ -12234,15 +12357,15 @@
       </c>
       <c r="J17" s="36">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="K17" s="36">
         <f t="shared" si="2"/>
-        <v>0.22400000000000003</v>
+        <v>0.15024091108190979</v>
       </c>
       <c r="L17" s="36">
         <f t="shared" si="1"/>
-        <v>0.22400000000000003</v>
+        <v>0.15024091108190979</v>
       </c>
       <c r="M17" s="25" t="s">
         <v>165</v>
@@ -12260,7 +12383,7 @@
       </c>
       <c r="Q17" s="25" t="str">
         <f>IF(H17=0,"MISSING COVERAGE",IF(O17=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$18,A17)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
-        <v>MISSING COVERAGE</v>
+        <v>REVIEWED LINK</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="22.8">
@@ -12291,7 +12414,7 @@
       </c>
       <c r="H18" s="37">
         <f>SUMIF(Coverage!$B$2:$B$18,A18,Coverage!$G$2:$G$18)</f>
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I18" s="37">
         <f>SUMIF(Coverage!$B$2:$B$18,A18,Coverage!$I$2:$I$18)</f>
@@ -12299,15 +12422,15 @@
       </c>
       <c r="J18" s="37">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="K18" s="37">
         <f t="shared" si="2"/>
-        <v>0.12</v>
+        <v>7.7084425799685385E-2</v>
       </c>
       <c r="L18" s="37">
         <f t="shared" si="1"/>
-        <v>1.7999999999999999E-2</v>
+        <v>1.1562663869952807E-2</v>
       </c>
       <c r="M18" s="26" t="s">
         <v>165</v>
@@ -12325,7 +12448,7 @@
       </c>
       <c r="Q18" s="26" t="str">
         <f>IF(H18=0,"MISSING COVERAGE",IF(O18=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$18,A18)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
-        <v>MISSING COVERAGE</v>
+        <v>REVIEWED LINK</v>
       </c>
     </row>
   </sheetData>

--- a/data/indonesia_model_inputs.xlsx
+++ b/data/indonesia_model_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/wrgg_uw_edu/Documents/02Work/WorldBank-Indonesia/uw-wb-indonesia-ncd/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_DC2E0DB659B3F61906DA456628709D9ECC8254F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E7A28FC-523C-415C-8B2E-3C381431A492}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_DC2E0DB659B3F61906DA456628709D9ECC8254F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8414A789-FA28-4929-A274-73F215098615}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -7684,7 +7684,7 @@
       <c r="G3" s="26">
         <v>0.1</v>
       </c>
-      <c r="H3" s="26"/>
+      <c r="H3" s="27"/>
       <c r="I3" s="33">
         <f>IF(H3="",Assumptions!$B$5,H3)</f>
         <v>0.8</v>
@@ -7747,7 +7747,7 @@
       <c r="G4" s="26">
         <v>0.31</v>
       </c>
-      <c r="H4" s="26"/>
+      <c r="H4" s="27"/>
       <c r="I4" s="33">
         <f>IF(H4="",Assumptions!$B$5,H4)</f>
         <v>0.8</v>
@@ -7810,7 +7810,7 @@
       <c r="G5" s="26">
         <v>0.31</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="27"/>
       <c r="I5" s="33">
         <f>IF(H5="",Assumptions!$B$5,H5)</f>
         <v>0.8</v>
@@ -7873,7 +7873,7 @@
       <c r="G6" s="26">
         <v>0.31</v>
       </c>
-      <c r="H6" s="26"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="33">
         <f>IF(H6="",Assumptions!$B$5,H6)</f>
         <v>0.8</v>
@@ -7936,7 +7936,7 @@
       <c r="G7" s="26">
         <v>0.31</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="27"/>
       <c r="I7" s="33">
         <f>IF(H7="",Assumptions!$B$5,H7)</f>
         <v>0.8</v>
@@ -7999,7 +7999,7 @@
       <c r="G8" s="26">
         <v>0.31</v>
       </c>
-      <c r="H8" s="26"/>
+      <c r="H8" s="27"/>
       <c r="I8" s="33">
         <f>IF(H8="",Assumptions!$B$5,H8)</f>
         <v>0.8</v>
@@ -8062,7 +8062,7 @@
       <c r="G9" s="26">
         <v>0.31</v>
       </c>
-      <c r="H9" s="26"/>
+      <c r="H9" s="27"/>
       <c r="I9" s="33">
         <f>IF(H9="",Assumptions!$B$5,H9)</f>
         <v>0.8</v>
@@ -8125,7 +8125,7 @@
       <c r="G10" s="26">
         <v>0.31</v>
       </c>
-      <c r="H10" s="26"/>
+      <c r="H10" s="27"/>
       <c r="I10" s="33">
         <f>IF(H10="",Assumptions!$B$5,H10)</f>
         <v>0.8</v>
@@ -8188,7 +8188,7 @@
       <c r="G11" s="26">
         <v>0.31</v>
       </c>
-      <c r="H11" s="26"/>
+      <c r="H11" s="27"/>
       <c r="I11" s="33">
         <f>IF(H11="",Assumptions!$B$5,H11)</f>
         <v>0.8</v>
@@ -8251,7 +8251,7 @@
       <c r="G12" s="26">
         <v>0.31</v>
       </c>
-      <c r="H12" s="26"/>
+      <c r="H12" s="27"/>
       <c r="I12" s="33">
         <f>IF(H12="",Assumptions!$B$5,H12)</f>
         <v>0.8</v>
@@ -8314,7 +8314,7 @@
       <c r="G13" s="26">
         <v>0.31</v>
       </c>
-      <c r="H13" s="26"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="33">
         <f>IF(H13="",Assumptions!$B$5,H13)</f>
         <v>0.8</v>
@@ -8377,7 +8377,7 @@
       <c r="G14" s="26">
         <v>0.31</v>
       </c>
-      <c r="H14" s="26"/>
+      <c r="H14" s="27"/>
       <c r="I14" s="33">
         <f>IF(H14="",Assumptions!$B$5,H14)</f>
         <v>0.8</v>
@@ -8440,7 +8440,7 @@
       <c r="G15" s="26">
         <v>0.31</v>
       </c>
-      <c r="H15" s="26"/>
+      <c r="H15" s="27"/>
       <c r="I15" s="33">
         <f>IF(H15="",Assumptions!$B$5,H15)</f>
         <v>0.8</v>
@@ -8503,7 +8503,7 @@
       <c r="G16" s="26">
         <v>0.31</v>
       </c>
-      <c r="H16" s="26"/>
+      <c r="H16" s="27"/>
       <c r="I16" s="33">
         <f>IF(H16="",Assumptions!$B$5,H16)</f>
         <v>0.8</v>
@@ -8566,7 +8566,7 @@
       <c r="G17" s="38">
         <v>0.31</v>
       </c>
-      <c r="H17" s="26"/>
+      <c r="H17" s="27"/>
       <c r="I17" s="33">
         <f>IF(H17="",Assumptions!$B$5,H17)</f>
         <v>0.8</v>
@@ -8625,7 +8625,7 @@
       <c r="G18" s="38">
         <v>0.31</v>
       </c>
-      <c r="H18" s="28"/>
+      <c r="H18" s="27"/>
       <c r="I18" s="34">
         <f>IF(H18="",Assumptions!$B$5,H18)</f>
         <v>0.8</v>

--- a/data/indonesia_model_inputs.xlsx
+++ b/data/indonesia_model_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/wrgg_uw_edu/Documents/02Work/WorldBank-Indonesia/uw-wb-indonesia-ncd/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_45329FAA1C5950AFA18B860B8102B22A93A6ACC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5DCF537-D55D-4731-AC69-4177EBDC4BD9}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_45329FAA1C5950AFA18B860B8102B22A93A6ACC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCC6E55B-2FE9-4B6D-A1A9-54BE5C9A9A4C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -67,13 +67,22 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={B1FEFC56-CF80-485C-B87E-A5E63818491E}</author>
     <author>tc={5282C296-63F9-415C-B2F2-3B273B7413D7}</author>
     <author>tc={D51D381D-3B39-435F-B5B2-6143D8D91563}</author>
     <author>tc={65F284AB-064D-4B9D-A390-F156B89E3B37}</author>
     <author>tc={8DE0ED5B-C37D-4E7B-B75F-DADA3DBFFB3B}</author>
   </authors>
   <commentList>
-    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{5282C296-63F9-415C-B2F2-3B273B7413D7}">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{B1FEFC56-CF80-485C-B87E-A5E63818491E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    PIN 10%, but *.41 because those are the severe cases</t>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="1" shapeId="0" xr:uid="{5282C296-63F9-415C-B2F2-3B273B7413D7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -81,7 +90,7 @@
     Raised from 6% to 30%</t>
       </text>
     </comment>
-    <comment ref="O8" authorId="1" shapeId="0" xr:uid="{D51D381D-3B39-435F-B5B2-6143D8D91563}">
+    <comment ref="O8" authorId="2" shapeId="0" xr:uid="{D51D381D-3B39-435F-B5B2-6143D8D91563}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -89,7 +98,7 @@
     Updated from 0</t>
       </text>
     </comment>
-    <comment ref="S33" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+    <comment ref="S33" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -97,7 +106,7 @@
     Pending update with Sali Info</t>
       </text>
     </comment>
-    <comment ref="L35" authorId="3" shapeId="0" xr:uid="{8DE0ED5B-C37D-4E7B-B75F-DADA3DBFFB3B}">
+    <comment ref="L35" authorId="4" shapeId="0" xr:uid="{8DE0ED5B-C37D-4E7B-B75F-DADA3DBFFB3B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -2199,7 +2208,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2617,20 +2626,33 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2653,36 +2675,23 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3341,6 +3350,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA9DEF6B-1F41-0FC3-6761-D6F769C9562E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3786,6 +3849,9 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="L3" dT="2026-08-28T21:04:09.70" personId="{AE4CD8BF-B03D-4C3B-B05E-44787D7972AD}" id="{B1FEFC56-CF80-485C-B87E-A5E63818491E}">
+    <text>PIN 10%, but *.41 because those are the severe cases</text>
+  </threadedComment>
   <threadedComment ref="L6" dT="2026-08-28T18:06:24.02" personId="{AE4CD8BF-B03D-4C3B-B05E-44787D7972AD}" id="{5282C296-63F9-415C-B2F2-3B273B7413D7}">
     <text>Raised from 6% to 30%</text>
   </threadedComment>
@@ -3818,38 +3884,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="A3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
@@ -3862,54 +3928,54 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75" t="s">
+      <c r="D5" s="66"/>
+      <c r="E5" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75" t="s">
+      <c r="F5" s="66"/>
+      <c r="G5" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="75"/>
+      <c r="H5" s="66"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="76" t="str">
+      <c r="A6" s="67" t="str">
         <f>IF(COUNTIF(QA_Checks!$E$2:$E$9,"FAIL")=0,"READY TO RUN","REVIEW REQUIRED")</f>
         <v>READY TO RUN</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="76">
+      <c r="B6" s="68"/>
+      <c r="C6" s="67">
         <f>COUNTA(Dictionaries!$A$2:$A$9)</f>
         <v>8</v>
       </c>
-      <c r="D6" s="77"/>
-      <c r="E6" s="76">
+      <c r="D6" s="68"/>
+      <c r="E6" s="67">
         <f>COUNTIF(Dictionaries!$I$2:$I$9,1)</f>
         <v>7</v>
       </c>
-      <c r="F6" s="77"/>
-      <c r="G6" s="76">
+      <c r="F6" s="68"/>
+      <c r="G6" s="67">
         <f>COUNTA(Intervention_Cause_Map!$A$2:$A$18)</f>
         <v>17</v>
       </c>
-      <c r="H6" s="77"/>
+      <c r="H6" s="68"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="78"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="79"/>
+      <c r="A7" s="69"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="70"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1"/>
@@ -3922,86 +3988,86 @@
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
     </row>
     <row r="10" spans="1:8" ht="28.05" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="69"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="74"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="72"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="77"/>
     </row>
     <row r="12" spans="1:8" ht="28.05" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="72"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="77"/>
     </row>
     <row r="13" spans="1:8" ht="28.05" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="72"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="77"/>
     </row>
     <row r="14" spans="1:8" ht="28.05" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="63" t="s">
+      <c r="B14" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="65"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="82"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
@@ -4014,86 +4080,86 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
     </row>
     <row r="17" spans="1:8" ht="28.05" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="78" t="s">
         <v>623</v>
       </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
     </row>
     <row r="18" spans="1:8" ht="28.05" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="78" t="s">
         <v>624</v>
       </c>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
     </row>
     <row r="19" spans="1:8" ht="28.05" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
     </row>
     <row r="20" spans="1:8" ht="28.05" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
     </row>
     <row r="21" spans="1:8" ht="28.05" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1"/>
@@ -4106,19 +4172,32 @@
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B13:H13"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:B5"/>
@@ -4129,19 +4208,6 @@
     <mergeCell ref="E6:F7"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H7"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4691,7 +4757,7 @@
       <c r="B4" t="s">
         <v>660</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="61">
         <v>46262</v>
       </c>
       <c r="D4" t="s">
@@ -4705,7 +4771,7 @@
       <c r="B5" t="s">
         <v>663</v>
       </c>
-      <c r="C5" s="81">
+      <c r="C5" s="61">
         <v>46263</v>
       </c>
       <c r="D5" t="s">
@@ -9297,7 +9363,8 @@
         <v>350</v>
       </c>
       <c r="L3" s="26">
-        <v>0.1</v>
+        <f>10%*0.41</f>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="M3" s="18" t="s">
         <v>359</v>
@@ -9766,7 +9833,7 @@
       <c r="N8" s="30">
         <v>1</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="62">
         <v>30</v>
       </c>
       <c r="P8" s="24">
@@ -9858,7 +9925,7 @@
       <c r="N9" s="30">
         <v>1</v>
       </c>
-      <c r="O9" s="82">
+      <c r="O9" s="62">
         <v>30</v>
       </c>
       <c r="P9" s="24">
@@ -9950,7 +10017,7 @@
       <c r="N10" s="30">
         <v>1</v>
       </c>
-      <c r="O10" s="82">
+      <c r="O10" s="62">
         <v>30</v>
       </c>
       <c r="P10" s="24">
@@ -10042,7 +10109,7 @@
       <c r="N11" s="30">
         <v>1</v>
       </c>
-      <c r="O11" s="82">
+      <c r="O11" s="62">
         <v>30</v>
       </c>
       <c r="P11" s="24">
@@ -12215,7 +12282,7 @@
       <c r="K35" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L35" s="83">
+      <c r="L35" s="63">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M35" s="5" t="s">
@@ -13966,14 +14033,14 @@
       <c r="F15" s="53"/>
     </row>
     <row r="17" spans="1:6" ht="34.049999999999997" customHeight="1">
-      <c r="A17" s="80" t="s">
+      <c r="A17" s="83" t="s">
         <v>546</v>
       </c>
-      <c r="B17" s="80"/>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/indonesia_model_inputs.xlsx
+++ b/data/indonesia_model_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/wrgg_uw_edu/Documents/02Work/WorldBank-Indonesia/uw-wb-indonesia-ncd/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{920901DE-702B-41BC-B411-40E8A243328F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BFFCAE2-3D5A-4694-9DC4-12BE27421482}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{920901DE-702B-41BC-B411-40E8A243328F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F2BE78B-F204-4CB0-974F-A8435D4333AC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -76,8 +76,10 @@
     <author>tc={B1FEFC56-CF80-485C-B87E-A5E63818491E}</author>
     <author>tc={5282C296-63F9-415C-B2F2-3B273B7413D7}</author>
     <author>tc={D51D381D-3B39-435F-B5B2-6143D8D91563}</author>
+    <author>tc={5AFDF6FE-756A-4F42-83A7-1275DBFFD219}</author>
     <author>tc={65F284AB-064D-4B9D-A390-F156B89E3B37}</author>
     <author>tc={8DE0ED5B-C37D-4E7B-B75F-DADA3DBFFB3B}</author>
+    <author>tc={84013A11-0436-47E2-A381-9E00FBF4B5A9}</author>
     <author>tc={C9810AFF-EA89-4031-BE73-C0FE3158C388}</author>
   </authors>
   <commentList>
@@ -105,7 +107,15 @@
     Updated from 0</t>
       </text>
     </comment>
-    <comment ref="S33" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
+    <comment ref="S8" authorId="3" shapeId="0" xr:uid="{5AFDF6FE-756A-4F42-83A7-1275DBFFD219}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This is set to 0 because it is included in acute MI</t>
+      </text>
+    </comment>
+    <comment ref="S33" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -113,7 +123,7 @@
     Pending update with Sali Info</t>
       </text>
     </comment>
-    <comment ref="L35" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
+    <comment ref="L35" authorId="5" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -123,14 +133,24 @@
     No exactly 0 to avoid numerica isues</t>
       </text>
     </comment>
-    <comment ref="S38" authorId="5" shapeId="0" xr:uid="{C9810AFF-EA89-4031-BE73-C0FE3158C388}">
+    <comment ref="S37" authorId="6" shapeId="0" xr:uid="{84013A11-0436-47E2-A381-9E00FBF4B5A9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    In expected value, insulin + non-insulin correspond to 82 dollars provided by Farizal</t>
+      </text>
+    </comment>
+    <comment ref="S38" authorId="7" shapeId="0" xr:uid="{C9810AFF-EA89-4031-BE73-C0FE3158C388}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     It was $643, assuming $1500 as per Farizal’s paper
 Reply:
-    $ $3000 quick internet search</t>
+    $ $3000 quick internet search
+Reply:
+    This new value comes from Farizal’s paper</t>
       </text>
     </comment>
   </commentList>
@@ -2212,7 +2232,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2289,6 +2309,12 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2713,23 +2739,27 @@
     <xf numFmtId="164" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2752,26 +2782,20 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2780,51 +2804,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="32">
     <dxf>
       <font>
         <b/>
@@ -3403,6 +3383,438 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{585BD83D-BA91-531F-98E7-657A00A4B847}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7734300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89772EA1-2814-B07A-980D-2DC5A1603633}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7734300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E8C964B-FAAB-C602-31F7-16A83C28A28F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7734300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A463DF7D-F401-16FD-7FF2-E2ED1DB5F788}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7734300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{366F6C11-7AE6-81F5-EFCA-CD415A246113}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7734300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3084563A-C1B2-664B-EF0C-382CADB67850}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7734300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA9B2F9D-1893-554D-46C3-2C5BCEFF9726}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7734300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CADB666-86FC-7893-77A6-D1569F0F6F30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7734300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3584,6 +3996,438 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DFA1D7C-F8C8-A410-A08B-FF0A11C86CA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7848600"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2314256F-0B28-A9F9-01F2-A0B58806E3D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7848600"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF5B1B65-9B3C-853C-585E-2CA64D3AA92B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7848600"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2E846C5-681C-4B24-C9C1-F274C8DD802B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7848600"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12272AB4-EF38-25E2-99AC-C9893BFB0520}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7848600"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8246A83D-5BB9-9D06-F73D-AD572EBC45A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7848600"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A32552CC-3D98-E182-9DD0-B344C389DB53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7848600"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BB11A03-79A0-8BD2-0C10-1A8498AB4166}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7848600"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61BBA270-2EF0-CE24-CE58-96A864EAE5C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4077,6 +4921,9 @@
   <threadedComment ref="O8" dT="2026-08-28T18:06:37.08" personId="{AE4CD8BF-B03D-4C3B-B05E-44787D7972AD}" id="{D51D381D-3B39-435F-B5B2-6143D8D91563}">
     <text>Updated from 0</text>
   </threadedComment>
+  <threadedComment ref="S8" dT="2026-09-01T01:30:26.75" personId="{EB2EF45A-97F9-4D8B-9B2F-13CF753F0281}" id="{5AFDF6FE-756A-4F42-83A7-1275DBFFD219}">
+    <text>This is set to 0 because it is included in acute MI</text>
+  </threadedComment>
   <threadedComment ref="S33" dT="2026-08-20T17:22:41.38" personId="{08755B68-3142-46D3-BD70-CECE36D4D0BB}" id="{65F284AB-064D-4B9D-A390-F156B89E3B37}">
     <text>Pending update with Sali Info</text>
   </threadedComment>
@@ -4086,11 +4933,17 @@
   <threadedComment ref="L35" dT="2026-08-28T18:08:10.08" personId="{AE4CD8BF-B03D-4C3B-B05E-44787D7972AD}" id="{E36F068F-91B3-47AE-9701-B3419D14CB4E}" parentId="{8DE0ED5B-C37D-4E7B-B75F-DADA3DBFFB3B}">
     <text>No exactly 0 to avoid numerica isues</text>
   </threadedComment>
+  <threadedComment ref="S37" dT="2026-09-01T00:09:18.44" personId="{EB2EF45A-97F9-4D8B-9B2F-13CF753F0281}" id="{84013A11-0436-47E2-A381-9E00FBF4B5A9}">
+    <text>In expected value, insulin + non-insulin correspond to 82 dollars provided by Farizal</text>
+  </threadedComment>
   <threadedComment ref="S38" dT="2026-08-30T15:15:16.34" personId="{EB2EF45A-97F9-4D8B-9B2F-13CF753F0281}" id="{C9810AFF-EA89-4031-BE73-C0FE3158C388}">
     <text>It was $643, assuming $1500 as per Farizal’s paper</text>
   </threadedComment>
   <threadedComment ref="S38" dT="2026-08-30T17:38:18.32" personId="{EB2EF45A-97F9-4D8B-9B2F-13CF753F0281}" id="{BE177651-E3AC-4A8A-BC40-578A8E99D79A}" parentId="{C9810AFF-EA89-4031-BE73-C0FE3158C388}">
     <text>$ $3000 quick internet search</text>
+  </threadedComment>
+  <threadedComment ref="S38" dT="2026-09-01T00:06:29.60" personId="{EB2EF45A-97F9-4D8B-9B2F-13CF753F0281}" id="{43E2D802-E62E-4A3D-B269-7B636D47AD5A}" parentId="{C9810AFF-EA89-4031-BE73-C0FE3158C388}">
+    <text>This new value comes from Farizal’s paper</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -4109,38 +4962,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
+      <c r="A3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
@@ -4153,54 +5006,54 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79" t="s">
+      <c r="D5" s="67"/>
+      <c r="E5" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79" t="s">
+      <c r="F5" s="67"/>
+      <c r="G5" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="79"/>
+      <c r="H5" s="67"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="80" t="str">
+      <c r="A6" s="68" t="str">
         <f>IF(COUNTIF(QA_Checks!$E$2:$E$9,"FAIL")=0,"READY TO RUN","REVIEW REQUIRED")</f>
         <v>READY TO RUN</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="80">
+      <c r="B6" s="69"/>
+      <c r="C6" s="68">
         <f>COUNTA(Dictionaries!$A$2:$A$10)</f>
         <v>9</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="80">
+      <c r="D6" s="69"/>
+      <c r="E6" s="68">
         <f>COUNTIF(Dictionaries!$I$2:$I$9,1)</f>
         <v>7</v>
       </c>
-      <c r="F6" s="81"/>
-      <c r="G6" s="80">
+      <c r="F6" s="69"/>
+      <c r="G6" s="68">
         <f>COUNTA(Intervention_Cause_Map!$A$2:$A$19)</f>
         <v>18</v>
       </c>
-      <c r="H6" s="81"/>
+      <c r="H6" s="69"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="82"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="83"/>
+      <c r="A7" s="70"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="71"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1"/>
@@ -4213,86 +5066,86 @@
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
     </row>
     <row r="10" spans="1:8" ht="28.05" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="73"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="75"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="76"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="78"/>
     </row>
     <row r="12" spans="1:8" ht="28.05" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="76"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="78"/>
     </row>
     <row r="13" spans="1:8" ht="28.05" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="76"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="78"/>
     </row>
     <row r="14" spans="1:8" ht="28.05" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="69"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="83"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
@@ -4305,86 +5158,86 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
     </row>
     <row r="17" spans="1:8" ht="28.05" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="65" t="s">
+      <c r="B17" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
     </row>
     <row r="18" spans="1:8" ht="28.05" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="65" t="s">
+      <c r="B18" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="79"/>
     </row>
     <row r="19" spans="1:8" ht="28.05" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="65" t="s">
+      <c r="B19" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="79"/>
     </row>
     <row r="20" spans="1:8" ht="28.05" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="79"/>
     </row>
     <row r="21" spans="1:8" ht="28.05" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="65"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1"/>
@@ -4397,19 +5250,32 @@
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B13:H13"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:B5"/>
@@ -4420,19 +5286,6 @@
     <mergeCell ref="E6:F7"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H7"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8308,16 +9161,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="containsText" dxfId="35" priority="1" operator="containsText" text="OK"/>
-    <cfRule type="containsText" dxfId="34" priority="3" operator="containsText" text="FAIL"/>
-    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="REVIEW"/>
-    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="BAD"/>
+    <cfRule type="containsText" dxfId="31" priority="1" operator="containsText" text="OK"/>
+    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="FAIL"/>
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="REVIEW"/>
+    <cfRule type="containsText" dxfId="28" priority="6" operator="containsText" text="BAD"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V19">
-    <cfRule type="containsText" dxfId="31" priority="7" operator="containsText" text="OK"/>
-    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="FAIL"/>
-    <cfRule type="containsText" dxfId="29" priority="11" operator="containsText" text="REVIEW"/>
-    <cfRule type="containsText" dxfId="28" priority="12" operator="containsText" text="BAD"/>
+    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="OK"/>
+    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="FAIL"/>
+    <cfRule type="containsText" dxfId="25" priority="11" operator="containsText" text="REVIEW"/>
+    <cfRule type="containsText" dxfId="24" priority="12" operator="containsText" text="BAD"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8428,7 +9281,7 @@
         <v>137</v>
       </c>
       <c r="G2" s="27">
-        <v>0.31</v>
+        <v>0.40110000000000001</v>
       </c>
       <c r="H2" s="27"/>
       <c r="I2" s="32">
@@ -8460,7 +9313,7 @@
       </c>
       <c r="Q2" s="32">
         <f t="shared" ref="Q2:Q18" si="0">IF(G2="","",I2-G2)</f>
-        <v>0.49000000000000005</v>
+        <v>0.39890000000000003</v>
       </c>
       <c r="R2" s="20">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B2)</f>
@@ -8491,7 +9344,7 @@
         <v>137</v>
       </c>
       <c r="G3" s="26">
-        <v>0.1</v>
+        <v>6.6400000000000001E-2</v>
       </c>
       <c r="H3" s="27"/>
       <c r="I3" s="33">
@@ -8523,7 +9376,7 @@
       </c>
       <c r="Q3" s="33">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.73360000000000003</v>
       </c>
       <c r="R3" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B3)</f>
@@ -8554,7 +9407,7 @@
         <v>144</v>
       </c>
       <c r="G4" s="26">
-        <v>0.31</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="H4" s="27"/>
       <c r="I4" s="33">
@@ -8586,7 +9439,7 @@
       </c>
       <c r="Q4" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.5534</v>
       </c>
       <c r="R4" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B4)</f>
@@ -8617,7 +9470,7 @@
         <v>150</v>
       </c>
       <c r="G5" s="26">
-        <v>0.31</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="33">
@@ -8649,7 +9502,7 @@
       </c>
       <c r="Q5" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.5534</v>
       </c>
       <c r="R5" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B5)</f>
@@ -8680,7 +9533,7 @@
         <v>156</v>
       </c>
       <c r="G6" s="26">
-        <v>0.31</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="33">
@@ -8712,7 +9565,7 @@
       </c>
       <c r="Q6" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.5534</v>
       </c>
       <c r="R6" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B6)</f>
@@ -8743,7 +9596,7 @@
         <v>161</v>
       </c>
       <c r="G7" s="26">
-        <v>0.31</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="33">
@@ -8775,7 +9628,7 @@
       </c>
       <c r="Q7" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.5534</v>
       </c>
       <c r="R7" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B7)</f>
@@ -8806,7 +9659,7 @@
         <v>144</v>
       </c>
       <c r="G8" s="26">
-        <v>0.31</v>
+        <v>0.53010000000000002</v>
       </c>
       <c r="H8" s="27"/>
       <c r="I8" s="33">
@@ -8838,7 +9691,7 @@
       </c>
       <c r="Q8" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.26990000000000003</v>
       </c>
       <c r="R8" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B8)</f>
@@ -8869,7 +9722,7 @@
         <v>150</v>
       </c>
       <c r="G9" s="26">
-        <v>0.31</v>
+        <v>0.38219999999999998</v>
       </c>
       <c r="H9" s="27"/>
       <c r="I9" s="33">
@@ -8901,7 +9754,7 @@
       </c>
       <c r="Q9" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.41780000000000006</v>
       </c>
       <c r="R9" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B9)</f>
@@ -8932,7 +9785,7 @@
         <v>156</v>
       </c>
       <c r="G10" s="26">
-        <v>0.31</v>
+        <v>0.21240000000000001</v>
       </c>
       <c r="H10" s="27"/>
       <c r="I10" s="33">
@@ -8964,7 +9817,7 @@
       </c>
       <c r="Q10" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.58760000000000001</v>
       </c>
       <c r="R10" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B10)</f>
@@ -8995,7 +9848,7 @@
         <v>144</v>
       </c>
       <c r="G11" s="26">
-        <v>0.31</v>
+        <v>0.26840000000000003</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="33">
@@ -9027,7 +9880,7 @@
       </c>
       <c r="Q11" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.53160000000000007</v>
       </c>
       <c r="R11" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B11)</f>
@@ -9058,7 +9911,7 @@
         <v>161</v>
       </c>
       <c r="G12" s="26">
-        <v>0.31</v>
+        <v>0.26840000000000003</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="33">
@@ -9090,7 +9943,7 @@
       </c>
       <c r="Q12" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.53160000000000007</v>
       </c>
       <c r="R12" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B12)</f>
@@ -9121,7 +9974,7 @@
         <v>167</v>
       </c>
       <c r="G13" s="26">
-        <v>0.31</v>
+        <v>0.26840000000000003</v>
       </c>
       <c r="H13" s="27"/>
       <c r="I13" s="33">
@@ -9153,7 +10006,7 @@
       </c>
       <c r="Q13" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.53160000000000007</v>
       </c>
       <c r="R13" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B13)</f>
@@ -9184,7 +10037,7 @@
         <v>144</v>
       </c>
       <c r="G14" s="26">
-        <v>0.31</v>
+        <v>0.50249999999999995</v>
       </c>
       <c r="H14" s="27"/>
       <c r="I14" s="33">
@@ -9216,7 +10069,7 @@
       </c>
       <c r="Q14" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.2975000000000001</v>
       </c>
       <c r="R14" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B14)</f>
@@ -9247,7 +10100,7 @@
         <v>161</v>
       </c>
       <c r="G15" s="26">
-        <v>0.31</v>
+        <v>0.50249999999999995</v>
       </c>
       <c r="H15" s="27"/>
       <c r="I15" s="33">
@@ -9279,7 +10132,7 @@
       </c>
       <c r="Q15" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.2975000000000001</v>
       </c>
       <c r="R15" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B15)</f>
@@ -9310,7 +10163,7 @@
         <v>167</v>
       </c>
       <c r="G16" s="26">
-        <v>0.31</v>
+        <v>0.50249999999999995</v>
       </c>
       <c r="H16" s="27"/>
       <c r="I16" s="33">
@@ -9342,7 +10195,7 @@
       </c>
       <c r="Q16" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.2975000000000001</v>
       </c>
       <c r="R16" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B16)</f>
@@ -9373,7 +10226,7 @@
         <v>172</v>
       </c>
       <c r="G17" s="38">
-        <v>0.16</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="H17" s="27"/>
       <c r="I17" s="33">
@@ -9405,7 +10258,7 @@
       </c>
       <c r="Q17" s="33">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0.58700000000000008</v>
       </c>
       <c r="R17" s="21">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B17)</f>
@@ -9436,7 +10289,7 @@
         <v>218</v>
       </c>
       <c r="G18" s="38">
-        <v>0.16</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="34">
@@ -9468,7 +10321,7 @@
       </c>
       <c r="Q18" s="34">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0.58700000000000008</v>
       </c>
       <c r="R18" s="22">
         <f>COUNTIF(Intervention_Cause_Map!$A$2:$A$19,B18)</f>
@@ -9544,16 +10397,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="P2:P19">
-    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="OK"/>
-    <cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="FAIL"/>
-    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="REVIEW"/>
-    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="BAD"/>
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="OK"/>
+    <cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="FAIL"/>
+    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="REVIEW"/>
+    <cfRule type="containsText" dxfId="20" priority="6" operator="containsText" text="BAD"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S19">
-    <cfRule type="containsText" dxfId="23" priority="7" operator="containsText" text="OK"/>
-    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="FAIL"/>
-    <cfRule type="containsText" dxfId="21" priority="11" operator="containsText" text="REVIEW"/>
-    <cfRule type="containsText" dxfId="20" priority="12" operator="containsText" text="BAD"/>
+    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="OK"/>
+    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="FAIL"/>
+    <cfRule type="containsText" dxfId="17" priority="11" operator="containsText" text="REVIEW"/>
+    <cfRule type="containsText" dxfId="16" priority="12" operator="containsText" text="BAD"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -9564,7 +10417,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -9737,7 +10590,7 @@
         <v>360</v>
       </c>
       <c r="S2" s="42">
-        <v>50.857353529999997</v>
+        <v>68.174792999999994</v>
       </c>
       <c r="T2" s="39">
         <v>2023</v>
@@ -9765,11 +10618,11 @@
         <v>1</v>
       </c>
       <c r="AB2" s="20">
-        <f t="shared" ref="AB2:AB35" si="0">SUMIF($B$2:$B$38,B2,$D$2:$D$38)</f>
+        <f t="shared" ref="AB2:AB38" si="0">SUMIF($B$2:$B$38,B2,$D$2:$D$38)</f>
         <v>1</v>
       </c>
       <c r="AC2" s="20" t="str">
-        <f t="shared" ref="AC2:AC34" si="1">IF(AA2&lt;1,"BAD KEY",IF(S2="","MISSING COST",IF(U2=0,"REVIEW ADJUSTMENT",IF(AB2&lt;&gt;1,"CHECK SELECTION","OK"))))</f>
+        <f t="shared" ref="AC2:AC38" si="1">IF(AA2&lt;1,"BAD KEY",IF(S2="","MISSING COST",IF(U2=0,"REVIEW ADJUSTMENT",IF(AB2&lt;&gt;1,"CHECK SELECTION","OK"))))</f>
         <v>OK</v>
       </c>
     </row>
@@ -9830,8 +10683,8 @@
       <c r="R3" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S3" s="43">
-        <v>12488.38616</v>
+      <c r="S3" s="42">
+        <v>3766.310954</v>
       </c>
       <c r="T3" s="40">
         <v>2023</v>
@@ -9878,7 +10731,7 @@
         <v>373</v>
       </c>
       <c r="D4" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>145</v>
@@ -9922,8 +10775,8 @@
       <c r="R4" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="S4" s="43">
-        <v>1.291584418</v>
+      <c r="S4" s="42">
+        <v>1.2915840000000001</v>
       </c>
       <c r="T4" s="40">
         <v>2023</v>
@@ -9970,7 +10823,7 @@
         <v>382</v>
       </c>
       <c r="D5" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>145</v>
@@ -10014,8 +10867,8 @@
       <c r="R5" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="S5" s="43">
-        <v>2.7665218579999999</v>
+      <c r="S5" s="42">
+        <v>2.7665220000000001</v>
       </c>
       <c r="T5" s="40">
         <v>2023</v>
@@ -10062,7 +10915,7 @@
         <v>373</v>
       </c>
       <c r="D6" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>145</v>
@@ -10106,8 +10959,8 @@
       <c r="R6" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="S6" s="43">
-        <v>22.22959981</v>
+      <c r="S6" s="42">
+        <v>69.304995000000005</v>
       </c>
       <c r="T6" s="40">
         <v>2023</v>
@@ -10154,7 +11007,7 @@
         <v>382</v>
       </c>
       <c r="D7" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>145</v>
@@ -10198,8 +11051,8 @@
       <c r="R7" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="S7" s="43">
-        <v>40.487718809999997</v>
+      <c r="S7" s="42">
+        <v>40.487718999999998</v>
       </c>
       <c r="T7" s="40">
         <v>2023</v>
@@ -10246,7 +11099,7 @@
         <v>373</v>
       </c>
       <c r="D8" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>151</v>
@@ -10290,8 +11143,8 @@
       <c r="R8" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S8" s="43">
-        <v>35.362648819999997</v>
+      <c r="S8" s="42">
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="T8" s="40">
         <v>2023</v>
@@ -10338,7 +11191,7 @@
         <v>382</v>
       </c>
       <c r="D9" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>151</v>
@@ -10382,8 +11235,8 @@
       <c r="R9" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S9" s="43">
-        <v>64.94344126</v>
+      <c r="S9" s="42">
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="T9" s="40">
         <v>2023</v>
@@ -10474,8 +11327,8 @@
       <c r="R10" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S10" s="43">
-        <v>119.7214874</v>
+      <c r="S10" s="42">
+        <v>77.628668000000005</v>
       </c>
       <c r="T10" s="40">
         <v>2023</v>
@@ -10566,8 +11419,8 @@
       <c r="R11" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S11" s="43">
-        <v>36.463998099999998</v>
+      <c r="S11" s="42">
+        <v>213.29056800000001</v>
       </c>
       <c r="T11" s="40">
         <v>2023</v>
@@ -10656,8 +11509,8 @@
       <c r="R12" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S12" s="43">
-        <v>186.47979240000001</v>
+      <c r="S12" s="42">
+        <v>574.50203999999997</v>
       </c>
       <c r="T12" s="40">
         <v>2023</v>
@@ -10702,7 +11555,7 @@
         <v>373</v>
       </c>
       <c r="D13" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="18" t="s">
         <v>157</v>
@@ -10746,8 +11599,8 @@
       <c r="R13" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S13" s="43">
-        <v>35.362648819999997</v>
+      <c r="S13" s="42">
+        <v>71.302158000000006</v>
       </c>
       <c r="T13" s="40">
         <v>2023</v>
@@ -10794,7 +11647,7 @@
         <v>382</v>
       </c>
       <c r="D14" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>157</v>
@@ -10838,8 +11691,8 @@
       <c r="R14" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S14" s="43">
-        <v>64.94344126</v>
+      <c r="S14" s="42">
+        <v>64.943441000000007</v>
       </c>
       <c r="T14" s="40">
         <v>2023</v>
@@ -10930,8 +11783,8 @@
       <c r="R15" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S15" s="43">
-        <v>119.7214874</v>
+      <c r="S15" s="42">
+        <v>172.27746099999999</v>
       </c>
       <c r="T15" s="40">
         <v>2023</v>
@@ -10976,7 +11829,7 @@
         <v>373</v>
       </c>
       <c r="D16" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>157</v>
@@ -11020,8 +11873,8 @@
       <c r="R16" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S16" s="43">
-        <v>550.94828949999999</v>
+      <c r="S16" s="42">
+        <v>1035.004856</v>
       </c>
       <c r="T16" s="40">
         <v>2023</v>
@@ -11068,7 +11921,7 @@
         <v>382</v>
       </c>
       <c r="D17" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="18" t="s">
         <v>157</v>
@@ -11112,8 +11965,8 @@
       <c r="R17" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S17" s="43">
-        <v>900.25859009999999</v>
+      <c r="S17" s="42">
+        <v>900.25859000000003</v>
       </c>
       <c r="T17" s="40">
         <v>2023</v>
@@ -11160,7 +12013,7 @@
         <v>373</v>
       </c>
       <c r="D18" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="18" t="s">
         <v>157</v>
@@ -11204,8 +12057,8 @@
       <c r="R18" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S18" s="43">
-        <v>35.362648819999997</v>
+      <c r="S18" s="42">
+        <v>56.227229000000001</v>
       </c>
       <c r="T18" s="40">
         <v>2023</v>
@@ -11252,7 +12105,7 @@
         <v>382</v>
       </c>
       <c r="D19" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>157</v>
@@ -11296,8 +12149,8 @@
       <c r="R19" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S19" s="43">
-        <v>64.94344126</v>
+      <c r="S19" s="42">
+        <v>64.943441000000007</v>
       </c>
       <c r="T19" s="40">
         <v>2023</v>
@@ -11388,8 +12241,8 @@
       <c r="R20" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S20" s="43">
-        <v>119.7214874</v>
+      <c r="S20" s="42">
+        <v>272.78860100000003</v>
       </c>
       <c r="T20" s="40">
         <v>2023</v>
@@ -11478,8 +12331,8 @@
       <c r="R21" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S21" s="64">
-        <v>475</v>
+      <c r="S21" s="42">
+        <v>575.48694599999999</v>
       </c>
       <c r="T21" s="40">
         <v>2023</v>
@@ -11568,8 +12421,8 @@
       <c r="R22" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S22" s="64">
-        <v>475</v>
+      <c r="S22" s="42">
+        <v>575.48694599999999</v>
       </c>
       <c r="T22" s="40">
         <v>2023</v>
@@ -11658,8 +12511,8 @@
       <c r="R23" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S23" s="64">
-        <v>475</v>
+      <c r="S23" s="42">
+        <v>575.48694599999999</v>
       </c>
       <c r="T23" s="40">
         <v>2023</v>
@@ -11748,8 +12601,8 @@
       <c r="R24" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S24" s="64">
-        <v>20</v>
+      <c r="S24" s="42">
+        <v>5.133311</v>
       </c>
       <c r="T24" s="40">
         <v>2023</v>
@@ -11794,7 +12647,7 @@
         <v>373</v>
       </c>
       <c r="D25" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="18" t="s">
         <v>168</v>
@@ -11838,8 +12691,8 @@
       <c r="R25" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S25" s="43">
-        <v>35.362648819999997</v>
+      <c r="S25" s="42">
+        <v>69.384409000000005</v>
       </c>
       <c r="T25" s="40">
         <v>2023</v>
@@ -11886,7 +12739,7 @@
         <v>382</v>
       </c>
       <c r="D26" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="18" t="s">
         <v>168</v>
@@ -11930,8 +12783,8 @@
       <c r="R26" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S26" s="43">
-        <v>64.94344126</v>
+      <c r="S26" s="42">
+        <v>64.943441000000007</v>
       </c>
       <c r="T26" s="40">
         <v>2023</v>
@@ -12022,8 +12875,8 @@
       <c r="R27" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S27" s="43">
-        <v>115.1062307</v>
+      <c r="S27" s="42">
+        <v>152.889884</v>
       </c>
       <c r="T27" s="40">
         <v>2023</v>
@@ -12112,8 +12965,8 @@
       <c r="R28" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S28" s="64">
-        <v>20</v>
+      <c r="S28" s="42">
+        <v>5.133311</v>
       </c>
       <c r="T28" s="40">
         <v>2023</v>
@@ -12158,7 +13011,7 @@
         <v>373</v>
       </c>
       <c r="D29" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>168</v>
@@ -12202,8 +13055,8 @@
       <c r="R29" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S29" s="43">
-        <v>35.362648819999997</v>
+      <c r="S29" s="42">
+        <v>69.384409000000005</v>
       </c>
       <c r="T29" s="40">
         <v>2023</v>
@@ -12250,7 +13103,7 @@
         <v>382</v>
       </c>
       <c r="D30" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>168</v>
@@ -12294,8 +13147,8 @@
       <c r="R30" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S30" s="43">
-        <v>64.94344126</v>
+      <c r="S30" s="42">
+        <v>64.943441000000007</v>
       </c>
       <c r="T30" s="40">
         <v>2023</v>
@@ -12386,8 +13239,8 @@
       <c r="R31" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S31" s="43">
-        <v>115.1062307</v>
+      <c r="S31" s="42">
+        <v>152.889884</v>
       </c>
       <c r="T31" s="40">
         <v>2023</v>
@@ -12478,8 +13331,8 @@
       <c r="R32" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S32" s="64">
-        <v>20</v>
+      <c r="S32" s="42">
+        <v>5.133311</v>
       </c>
       <c r="T32" s="40">
         <v>2023</v>
@@ -12568,8 +13421,8 @@
       <c r="R33" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S33" s="45">
-        <v>7</v>
+      <c r="S33" s="42">
+        <v>69.384409000000005</v>
       </c>
       <c r="T33" s="40">
         <v>2023</v>
@@ -12599,7 +13452,7 @@
         <v>1</v>
       </c>
       <c r="AC33" s="21" t="str">
-        <f>IF(AA33&lt;1,"BAD KEY",IF(S33="","MISSING COST",IF(U33=0,"REVIEW ADJUSTMENT",IF(AB33&lt;&gt;1,"CHECK SELECTION","OK"))))</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
@@ -12658,8 +13511,8 @@
       <c r="R34" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="S34" s="43">
-        <v>29.216219469999999</v>
+      <c r="S34" s="42">
+        <v>152.889884</v>
       </c>
       <c r="T34" s="40">
         <v>2023</v>
@@ -12781,7 +13634,7 @@
         <v>1</v>
       </c>
       <c r="AC35" s="22" t="str">
-        <f>IF(AA35&lt;1,"BAD KEY",IF(S35="","MISSING COST",IF(U35=0,"REVIEW ADJUSTMENT",IF(AB35&lt;&gt;1,"CHECK SELECTION","OK"))))</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
@@ -12841,7 +13694,7 @@
         <v>360</v>
       </c>
       <c r="S36" s="43">
-        <v>752.57623226071905</v>
+        <v>82.68</v>
       </c>
       <c r="T36" s="40">
         <v>2023</v>
@@ -12869,11 +13722,11 @@
         <v>2</v>
       </c>
       <c r="AB36" s="21">
-        <f>SUMIF($B$2:$B$38,B36,$D$2:$D$38)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC36" s="21" t="str">
-        <f>IF(AA36&lt;1,"BAD KEY",IF(S36="","MISSING COST",IF(U36=0,"REVIEW ADJUSTMENT",IF(AB36&lt;&gt;1,"CHECK SELECTION","OK"))))</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
@@ -12933,7 +13786,7 @@
         <v>360</v>
       </c>
       <c r="S37" s="43">
-        <v>1154.0355216616899</v>
+        <v>82.68</v>
       </c>
       <c r="T37" s="40">
         <v>2023</v>
@@ -12961,11 +13814,11 @@
         <v>2</v>
       </c>
       <c r="AB37" s="21">
-        <f>SUMIF($B$2:$B$38,B37,$D$2:$D$38)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC37" s="21" t="str">
-        <f>IF(AA37&lt;1,"BAD KEY",IF(S37="","MISSING COST",IF(U37=0,"REVIEW ADJUSTMENT",IF(AB37&lt;&gt;1,"CHECK SELECTION","OK"))))</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
@@ -13025,7 +13878,7 @@
         <v>368</v>
       </c>
       <c r="S38" s="45">
-        <v>3000</v>
+        <v>1718.8</v>
       </c>
       <c r="T38" s="40">
         <v>2023</v>
@@ -13053,26 +13906,26 @@
         <v>1</v>
       </c>
       <c r="AB38" s="21">
-        <f>SUMIF($B$2:$B$38,B38,$D$2:$D$38)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AC38" s="21" t="str">
-        <f>IF(AA38&lt;1,"BAD KEY",IF(S38="","MISSING COST",IF(U38=0,"REVIEW ADJUSTMENT",IF(AB38&lt;&gt;1,"CHECK SELECTION","OK"))))</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
+    <row r="41" spans="1:29">
+      <c r="S41" s="64"/>
+    </row>
+    <row r="43" spans="1:29">
+      <c r="S43" s="64"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="Y2:Y38">
-    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="OK"/>
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="FAIL"/>
-    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="REVIEW"/>
-    <cfRule type="containsText" dxfId="16" priority="6" operator="containsText" text="BAD"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC2:AC38">
-    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="OK"/>
-    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="FAIL"/>
-    <cfRule type="containsText" dxfId="13" priority="11" operator="containsText" text="REVIEW"/>
-    <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text="BAD"/>
+  <conditionalFormatting sqref="Y2:Y38 AC2:AC38">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="OK"/>
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="FAIL"/>
+    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="REVIEW"/>
+    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="BAD"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="D2:D35" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -13192,7 +14045,7 @@
       </c>
       <c r="H2" s="32">
         <f>SUMIF(Coverage!$B$2:$B$19,A2,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.40110000000000001</v>
       </c>
       <c r="I2" s="32">
         <f>SUMIF(Coverage!$B$2:$B$19,A2,Coverage!$I$2:$I$19)</f>
@@ -13200,15 +14053,15 @@
       </c>
       <c r="J2" s="32">
         <f t="shared" ref="J2:J18" si="0">IF(H2="","",I2-H2)</f>
-        <v>0.49000000000000005</v>
+        <v>0.39890000000000003</v>
       </c>
       <c r="K2" s="32">
         <f>IF(OR(H2="",F2=""),"",F2*J2/(1-F2*H2))</f>
-        <v>0.32489451476793257</v>
+        <v>0.28149397930446057</v>
       </c>
       <c r="L2" s="32">
         <f t="shared" ref="L2:L18" si="1">IF(K2="","",K2*G2)</f>
-        <v>0.32489451476793257</v>
+        <v>0.28149397930446057</v>
       </c>
       <c r="M2" s="20" t="s">
         <v>189</v>
@@ -13222,7 +14075,7 @@
       </c>
       <c r="P2" s="48">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M2,Cost_Components!$D$2:$D$38,1)</f>
-        <v>50.857353529999997</v>
+        <v>68.174792999999994</v>
       </c>
       <c r="Q2" s="20" t="str">
         <f>IF(H2=0,"MISSING COVERAGE",IF(O2=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A2)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13257,7 +14110,7 @@
       </c>
       <c r="H3" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A3,Coverage!$G$2:$G$19)</f>
-        <v>0.1</v>
+        <v>6.6400000000000001E-2</v>
       </c>
       <c r="I3" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A3,Coverage!$I$2:$I$19)</f>
@@ -13265,15 +14118,15 @@
       </c>
       <c r="J3" s="33">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.73360000000000003</v>
       </c>
       <c r="K3" s="33">
         <f t="shared" ref="K3:K18" si="2">IF(OR(H3="",F3=""),"",F3*J3/(1-F3*H3))</f>
-        <v>0.56756756756756754</v>
+        <v>0.57903599242264781</v>
       </c>
       <c r="L3" s="33">
         <f>IF(K3="","",K3*G3)</f>
-        <v>5.675675675675676E-2</v>
+        <v>5.7903599242264785E-2</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>192</v>
@@ -13287,7 +14140,7 @@
       </c>
       <c r="P3" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M3,Cost_Components!$D$2:$D$38,1)</f>
-        <v>12488.38616</v>
+        <v>3766.310954</v>
       </c>
       <c r="Q3" s="21" t="str">
         <f>IF(H3=0,"MISSING COVERAGE",IF(O3=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A3)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13322,7 +14175,7 @@
       </c>
       <c r="H4" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A4,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="I4" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A4,Coverage!$I$2:$I$19)</f>
@@ -13330,15 +14183,15 @@
       </c>
       <c r="J4" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.5534</v>
       </c>
       <c r="K4" s="33">
         <f t="shared" si="2"/>
-        <v>0.34650085345037795</v>
+        <v>0.37454199203707933</v>
       </c>
       <c r="L4" s="33">
         <f>IF(K4="","",K4*G4)</f>
-        <v>0.27720068276030235</v>
+        <v>0.29963359362966346</v>
       </c>
       <c r="M4" s="21" t="s">
         <v>195</v>
@@ -13352,7 +14205,7 @@
       </c>
       <c r="P4" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M4,Cost_Components!$D$2:$D$38,1)</f>
-        <v>43.254240667999994</v>
+        <v>70.596579000000006</v>
       </c>
       <c r="Q4" s="21" t="str">
         <f>IF(H4=0,"MISSING COVERAGE",IF(O4=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A4)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13387,7 +14240,7 @@
       </c>
       <c r="H5" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A5,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="I5" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A5,Coverage!$I$2:$I$19)</f>
@@ -13395,15 +14248,15 @@
       </c>
       <c r="J5" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.5534</v>
       </c>
       <c r="K5" s="33">
         <f>IF(OR(H5="",F5=""),"",F5*J5/(1-F5*H5))</f>
-        <v>0.31779966370405965</v>
+        <v>0.34474341167187345</v>
       </c>
       <c r="L5" s="33">
         <f t="shared" si="1"/>
-        <v>0.25423973096324776</v>
+        <v>0.27579472933749877</v>
       </c>
       <c r="M5" s="21" t="s">
         <v>195</v>
@@ -13417,7 +14270,7 @@
       </c>
       <c r="P5" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M5,Cost_Components!$D$2:$D$38,1)</f>
-        <v>43.254240667999994</v>
+        <v>70.596579000000006</v>
       </c>
       <c r="Q5" s="21" t="str">
         <f>IF(H5=0,"MISSING COVERAGE",IF(O5=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A5)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13452,7 +14305,7 @@
       </c>
       <c r="H6" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A6,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="I6" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A6,Coverage!$I$2:$I$19)</f>
@@ -13460,15 +14313,15 @@
       </c>
       <c r="J6" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.5534</v>
       </c>
       <c r="K6" s="33">
         <f t="shared" si="2"/>
-        <v>0.28310340761702629</v>
+        <v>0.30843549454824232</v>
       </c>
       <c r="L6" s="33">
         <f t="shared" si="1"/>
-        <v>0.22648272609362105</v>
+        <v>0.24674839563859385</v>
       </c>
       <c r="M6" s="21" t="s">
         <v>195</v>
@@ -13482,7 +14335,7 @@
       </c>
       <c r="P6" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M6,Cost_Components!$D$2:$D$38,1)</f>
-        <v>43.254240667999994</v>
+        <v>70.596579000000006</v>
       </c>
       <c r="Q6" s="21" t="str">
         <f>IF(H6=0,"MISSING COVERAGE",IF(O6=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A6)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13517,7 +14370,7 @@
       </c>
       <c r="H7" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A7,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="I7" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A7,Coverage!$I$2:$I$19)</f>
@@ -13525,15 +14378,15 @@
       </c>
       <c r="J7" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.5534</v>
       </c>
       <c r="K7" s="33">
         <f t="shared" si="2"/>
-        <v>0.26957743181552146</v>
+        <v>0.29419589231058091</v>
       </c>
       <c r="L7" s="33">
         <f t="shared" si="1"/>
-        <v>0.26957743181552146</v>
+        <v>0.29419589231058091</v>
       </c>
       <c r="M7" s="21" t="s">
         <v>195</v>
@@ -13547,7 +14400,7 @@
       </c>
       <c r="P7" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M7,Cost_Components!$D$2:$D$38,1)</f>
-        <v>43.254240667999994</v>
+        <v>70.596579000000006</v>
       </c>
       <c r="Q7" s="21" t="str">
         <f>IF(H7=0,"MISSING COVERAGE",IF(O7=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A7)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13582,7 +14435,7 @@
       </c>
       <c r="H8" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A8,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.53010000000000002</v>
       </c>
       <c r="I8" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A8,Coverage!$I$2:$I$19)</f>
@@ -13590,15 +14443,15 @@
       </c>
       <c r="J8" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.26990000000000003</v>
       </c>
       <c r="K8" s="33">
         <f t="shared" si="2"/>
-        <v>0.34810461759229211</v>
+        <v>0.22727984483344213</v>
       </c>
       <c r="L8" s="33">
         <f t="shared" si="1"/>
-        <v>6.962092351845843E-2</v>
+        <v>4.545596896668843E-2</v>
       </c>
       <c r="M8" s="21" t="s">
         <v>201</v>
@@ -13612,7 +14465,7 @@
       </c>
       <c r="P8" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M8,Cost_Components!$D$2:$D$38,1)</f>
-        <v>221.12892675999998</v>
+        <v>290.91923610000003</v>
       </c>
       <c r="Q8" s="21" t="str">
         <f>IF(H8=0,"MISSING COVERAGE",IF(O8=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A8)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13647,7 +14500,7 @@
       </c>
       <c r="H9" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A9,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.38219999999999998</v>
       </c>
       <c r="I9" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A9,Coverage!$I$2:$I$19)</f>
@@ -13655,15 +14508,15 @@
       </c>
       <c r="J9" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.41780000000000006</v>
       </c>
       <c r="K9" s="33">
         <f t="shared" si="2"/>
-        <v>0.12135242812533652</v>
+        <v>0.10535536907380162</v>
       </c>
       <c r="L9" s="33">
         <f t="shared" si="1"/>
-        <v>2.4270485625067305E-2</v>
+        <v>2.1071073814760324E-2</v>
       </c>
       <c r="M9" s="21" t="s">
         <v>203</v>
@@ -13677,7 +14530,7 @@
       </c>
       <c r="P9" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M9,Cost_Components!$D$2:$D$38,1)</f>
-        <v>371.14472105999999</v>
+        <v>818.08165899999995</v>
       </c>
       <c r="Q9" s="21" t="str">
         <f>IF(H9=0,"MISSING COVERAGE",IF(O9=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A9)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13712,7 +14565,7 @@
       </c>
       <c r="H10" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A10,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.21240000000000001</v>
       </c>
       <c r="I10" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A10,Coverage!$I$2:$I$19)</f>
@@ -13720,15 +14573,15 @@
       </c>
       <c r="J10" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.58760000000000001</v>
       </c>
       <c r="K10" s="33">
         <f t="shared" si="2"/>
-        <v>4.0196882690730115E-2</v>
+        <v>4.7820567075751164E-2</v>
       </c>
       <c r="L10" s="33">
         <f t="shared" si="1"/>
-        <v>8.0393765381460234E-3</v>
+        <v>9.5641134151502327E-3</v>
       </c>
       <c r="M10" s="21" t="s">
         <v>205</v>
@@ -13742,7 +14595,7 @@
       </c>
       <c r="P10" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M10,Cost_Components!$D$2:$D$38,1)</f>
-        <v>1084.92351876</v>
+        <v>1364.0206860000001</v>
       </c>
       <c r="Q10" s="21" t="str">
         <f>IF(H10=0,"MISSING COVERAGE",IF(O10=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A10)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13777,7 +14630,7 @@
       </c>
       <c r="H11" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A11,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.26840000000000003</v>
       </c>
       <c r="I11" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A11,Coverage!$I$2:$I$19)</f>
@@ -13785,15 +14638,15 @@
       </c>
       <c r="J11" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.53160000000000007</v>
       </c>
       <c r="K11" s="33">
         <f t="shared" si="2"/>
-        <v>9.3412412624443969E-2</v>
+        <v>0.10054555694723483</v>
       </c>
       <c r="L11" s="33">
         <f t="shared" si="1"/>
-        <v>4.670620631222199E-3</v>
+        <v>5.0272778473617417E-3</v>
       </c>
       <c r="M11" s="21" t="s">
         <v>206</v>
@@ -13807,7 +14660,7 @@
       </c>
       <c r="P11" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M11,Cost_Components!$D$2:$D$38,1)</f>
-        <v>475</v>
+        <v>575.48694599999999</v>
       </c>
       <c r="Q11" s="21" t="str">
         <f>IF(H11=0,"MISSING COVERAGE",IF(O11=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A11)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13842,7 +14695,7 @@
       </c>
       <c r="H12" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A12,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.26840000000000003</v>
       </c>
       <c r="I12" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A12,Coverage!$I$2:$I$19)</f>
@@ -13850,15 +14703,15 @@
       </c>
       <c r="J12" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.53160000000000007</v>
       </c>
       <c r="K12" s="33">
         <f t="shared" si="2"/>
-        <v>0.47054243446664945</v>
+        <v>0.49088077625707538</v>
       </c>
       <c r="L12" s="33">
         <f t="shared" si="1"/>
-        <v>9.4108486893329901E-2</v>
+        <v>9.8176155251415084E-2</v>
       </c>
       <c r="M12" s="21" t="s">
         <v>208</v>
@@ -13872,7 +14725,7 @@
       </c>
       <c r="P12" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M12,Cost_Components!$D$2:$D$38,1)</f>
-        <v>475</v>
+        <v>575.48694599999999</v>
       </c>
       <c r="Q12" s="21" t="str">
         <f>IF(H12=0,"MISSING COVERAGE",IF(O12=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A12)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13907,7 +14760,7 @@
       </c>
       <c r="H13" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A13,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.26840000000000003</v>
       </c>
       <c r="I13" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A13,Coverage!$I$2:$I$19)</f>
@@ -13915,15 +14768,15 @@
       </c>
       <c r="J13" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.53160000000000007</v>
       </c>
       <c r="K13" s="33">
         <f t="shared" si="2"/>
-        <v>0.47054243446664945</v>
+        <v>0.49088077625707538</v>
       </c>
       <c r="L13" s="33">
         <f t="shared" si="1"/>
-        <v>9.4108486893329901E-2</v>
+        <v>9.8176155251415084E-2</v>
       </c>
       <c r="M13" s="21" t="s">
         <v>210</v>
@@ -13937,7 +14790,7 @@
       </c>
       <c r="P13" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M13,Cost_Components!$D$2:$D$38,1)</f>
-        <v>475</v>
+        <v>575.48694599999999</v>
       </c>
       <c r="Q13" s="21" t="str">
         <f>IF(H13=0,"MISSING COVERAGE",IF(O13=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A13)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -13972,7 +14825,7 @@
       </c>
       <c r="H14" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A14,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.50249999999999995</v>
       </c>
       <c r="I14" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A14,Coverage!$I$2:$I$19)</f>
@@ -13980,15 +14833,15 @@
       </c>
       <c r="J14" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.2975000000000001</v>
       </c>
       <c r="K14" s="33">
         <f t="shared" si="2"/>
-        <v>4.6922783858644734E-2</v>
+        <v>2.9023857416727212E-2</v>
       </c>
       <c r="L14" s="33">
         <f t="shared" si="1"/>
-        <v>9.3845567717289469E-3</v>
+        <v>5.8047714833454429E-3</v>
       </c>
       <c r="M14" s="21" t="s">
         <v>212</v>
@@ -14002,7 +14855,7 @@
       </c>
       <c r="P14" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M14,Cost_Components!$D$2:$D$38,1)</f>
-        <v>56.216219469999999</v>
+        <v>227.40760399999999</v>
       </c>
       <c r="Q14" s="21" t="str">
         <f>IF(H14=0,"MISSING COVERAGE",IF(O14=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A14)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -14037,7 +14890,7 @@
       </c>
       <c r="H15" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A15,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.50249999999999995</v>
       </c>
       <c r="I15" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A15,Coverage!$I$2:$I$19)</f>
@@ -14045,15 +14898,15 @@
       </c>
       <c r="J15" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.2975000000000001</v>
       </c>
       <c r="K15" s="33">
         <f t="shared" si="2"/>
-        <v>0.14730800765236407</v>
+        <v>9.4930741895714016E-2</v>
       </c>
       <c r="L15" s="33">
         <f t="shared" si="1"/>
-        <v>0.11784640612189126</v>
+        <v>7.5944593516571221E-2</v>
       </c>
       <c r="M15" s="21" t="s">
         <v>213</v>
@@ -14067,7 +14920,7 @@
       </c>
       <c r="P15" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M15,Cost_Components!$D$2:$D$38,1)</f>
-        <v>200.04967196000001</v>
+        <v>227.40760399999999</v>
       </c>
       <c r="Q15" s="21" t="str">
         <f>IF(H15=0,"MISSING COVERAGE",IF(O15=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A15)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -14102,7 +14955,7 @@
       </c>
       <c r="H16" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A16,Coverage!$G$2:$G$19)</f>
-        <v>0.31</v>
+        <v>0.50249999999999995</v>
       </c>
       <c r="I16" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A16,Coverage!$I$2:$I$19)</f>
@@ -14110,15 +14963,15 @@
       </c>
       <c r="J16" s="33">
         <f t="shared" si="0"/>
-        <v>0.49000000000000005</v>
+        <v>0.2975000000000001</v>
       </c>
       <c r="K16" s="33">
         <f t="shared" si="2"/>
-        <v>0.31497649429147084</v>
+        <v>0.21824104234527694</v>
       </c>
       <c r="L16" s="33">
         <f t="shared" si="1"/>
-        <v>0.25198119543317671</v>
+        <v>0.17459283387622157</v>
       </c>
       <c r="M16" s="21" t="s">
         <v>214</v>
@@ -14132,7 +14985,7 @@
       </c>
       <c r="P16" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M16,Cost_Components!$D$2:$D$38,1)</f>
-        <v>200.04967196000001</v>
+        <v>227.40760399999999</v>
       </c>
       <c r="Q16" s="21" t="str">
         <f>IF(H16=0,"MISSING COVERAGE",IF(O16=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A16)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -14167,7 +15020,7 @@
       </c>
       <c r="H17" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A17,Coverage!$G$2:$G$19)</f>
-        <v>0.16</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="I17" s="33">
         <f>SUMIF(Coverage!$B$2:$B$19,A17,Coverage!$I$2:$I$19)</f>
@@ -14175,15 +15028,15 @@
       </c>
       <c r="J17" s="33">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0.58700000000000008</v>
       </c>
       <c r="K17" s="33">
         <f t="shared" si="2"/>
-        <v>0.18760469011725295</v>
+        <v>0.17478412522863587</v>
       </c>
       <c r="L17" s="33">
         <f t="shared" si="1"/>
-        <v>0.18760469011725295</v>
+        <v>0.17478412522863587</v>
       </c>
       <c r="M17" s="21" t="s">
         <v>215</v>
@@ -14197,7 +15050,7 @@
       </c>
       <c r="P17" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M17,Cost_Components!$D$2:$D$38,1)</f>
-        <v>1907.3167124006286</v>
+        <v>166.06495847821975</v>
       </c>
       <c r="Q17" s="21" t="str">
         <f>IF(H17=0,"MISSING COVERAGE",IF(O17=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A17)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -14232,7 +15085,7 @@
       </c>
       <c r="H18" s="34">
         <f>SUMIF(Coverage!$B$2:$B$19,A18,Coverage!$G$2:$G$19)</f>
-        <v>0.16</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="I18" s="34">
         <f>SUMIF(Coverage!$B$2:$B$19,A18,Coverage!$I$2:$I$19)</f>
@@ -14240,15 +15093,15 @@
       </c>
       <c r="J18" s="34">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0.58700000000000008</v>
       </c>
       <c r="K18" s="34">
         <f t="shared" si="2"/>
-        <v>9.8360655737704916E-2</v>
+        <v>9.0956045658798626E-2</v>
       </c>
       <c r="L18" s="34">
         <f t="shared" si="1"/>
-        <v>1.4754098360655736E-2</v>
+        <v>1.3643406848819794E-2</v>
       </c>
       <c r="M18" s="22" t="s">
         <v>215</v>
@@ -14262,7 +15115,7 @@
       </c>
       <c r="P18" s="50">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M18,Cost_Components!$D$2:$D$38,1)</f>
-        <v>1907.3167124006286</v>
+        <v>166.06495847821975</v>
       </c>
       <c r="Q18" s="22" t="str">
         <f>IF(H18=0,"MISSING COVERAGE",IF(O18=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A18)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
@@ -14327,7 +15180,7 @@
       </c>
       <c r="P19" s="49">
         <f>SUMIFS(Cost_Components!$S$2:$S$38,Cost_Components!$G$2:$G$38,M19,Cost_Components!$D$2:$D$38,1)</f>
-        <v>3000</v>
+        <v>1718.8</v>
       </c>
       <c r="Q19" s="21" t="str">
         <f>IF(H19=0,"MISSING COVERAGE",IF(O19=0,"REVIEW COST",IF(COUNTIF(Effect_Sizes!$B$2:$B$19,A19)&lt;&gt;1,"BAD EFFECT KEY","REVIEWED LINK")))</f>
